--- a/data/raw/PSY_age_of_onset.xlsx
+++ b/data/raw/PSY_age_of_onset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giaco\Desktop\Git_META\META\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C38632-8BAC-45E4-A296-D204B3F2A8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A200DAD0-C708-48DE-BF6F-88A12391B938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,9 +60,6 @@
     <t>CHR</t>
   </si>
   <si>
-    <t>PTSD</t>
-  </si>
-  <si>
     <t>median</t>
   </si>
   <si>
@@ -82,6 +79,9 @@
   </si>
   <si>
     <t>39.9</t>
+  </si>
+  <si>
+    <t>PD</t>
   </si>
 </sst>
 </file>
@@ -443,13 +443,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -579,7 +579,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -596,30 +596,30 @@
         <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2">
         <v>15.5</v>
       </c>
       <c r="C11">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
